--- a/08_cnn/excel_cnn_demo.xlsx
+++ b/08_cnn/excel_cnn_demo.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,8 +72,16 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -100,8 +108,23 @@
         <fgColor rgb="00FFF7CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F4EF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F6F9F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -137,11 +160,25 @@
         <color rgb="00D6B656"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9E2EF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9E2EF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2EF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2EF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -196,6 +233,33 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -565,7 +629,7 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="74" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -580,7 +644,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>ExcelをUIにして、外部PythonがWorkbookの値を読み、計算結果をDataFrameで返します。</t>
+          <t>画像行列にフィルタを重ね、paddingとstrideを変えながら特徴マップがどう変わるかを確認します。</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -612,7 +676,7 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>今回のゴール</t>
+          <t>01_INPUT の画像行列、フィルタ、display_mode、stride、paddingを変更してPythonを再実行します。</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
@@ -624,7 +688,7 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>Pythonが読む範囲</t>
+          <t>display_mode は feature / window / summary / exam から選びます。</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
@@ -656,22 +720,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
           <t>第8回 CNN: 入力と設定</t>
@@ -687,10 +751,10 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="34" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>このシートの表をPythonが xl(...) で読みます。値や設定を変えて結果の変化を確認します。</t>
+          <t>このシートの表をPythonが xl(...) で読みます。画像、フィルタ、padding、strideを変えて特徴マップの変化を確認します。</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -703,7 +767,7 @@
       <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="n"/>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
@@ -715,8 +779,8 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>画像行列</t>
         </is>
@@ -724,14 +788,14 @@
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="2" t="n"/>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>フィルタ</t>
         </is>
       </c>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="2" t="n"/>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>畳み込み設定</t>
         </is>
@@ -739,7 +803,7 @@
       <c r="I4" s="5" t="n"/>
       <c r="J4" s="5" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="n"/>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
@@ -751,106 +815,128 @@
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="n">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="20" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="2" t="n"/>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n"/>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>setting</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="2" t="n"/>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="22" t="n">
         <v>-1</v>
       </c>
       <c r="G7" s="2" t="n"/>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>display_mode</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr">
-        <is>
-          <t>リストから選択: feature / window / exam</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t>リストから選択: feature / window / summary / exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
       <c r="G8" s="2" t="n"/>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t>stride</t>
         </is>
       </c>
-      <c r="I8" s="14" t="n">
+      <c r="I8" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="14" t="inlineStr">
-        <is>
-          <t>教材では1固定</t>
-        </is>
-      </c>
-    </row>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>フィルタを動かすマス数</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>padding</t>
+        </is>
+      </c>
+      <c r="I9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="26" t="inlineStr">
+        <is>
+          <t>画像の外側に足す0の幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1"/>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="I7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="リストから選択してください" error="このセルは手入力ではなく、右側のリストから選択します。" promptTitle="選択式の設定" prompt="候補から選ぶと、Pythonの返す表や計算条件が切り替わります。" type="list">
-      <formula1>"feature,window,exam"</formula1>
+  <dataValidations count="3">
+    <dataValidation sqref="I7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"feature,window,summary,exam"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"0,1"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -867,7 +953,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -881,7 +967,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>このシートはPython in Excelの実行手順だけを置きます。概念説明はスライドとREADMEで確認します。</t>
+          <t>このシートは実行手順だけを置きます。概念説明はスライドとREADMEで確認します。</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -944,7 +1030,7 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>01_INPUT の値や display_mode を変えて再実行する</t>
+          <t>01_INPUT の display_mode を feature / window / summary / exam に変えて再実行する</t>
         </is>
       </c>
     </row>
